--- a/data/berita_antara_2026-08-02.xlsx
+++ b/data/berita_antara_2026-08-02.xlsx
@@ -476,28 +476,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>John Herdman: Laga lawan Vietnam peluang Indonesia ambil kendali grup</t>
+          <t>Leo/Daniel amankan gelar juaraTaipei Open 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 20:58:18 +0700</t>
+          <t>Sun, 02 Aug 2026 15:12:06 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional Indonesia John Herdman menyebut laga skuadnya menghadapi Vietnam pada lanjutan ...</t>
+          <t>Pebulu tangkis ganda putra Indonesia Leo Rolly Carnando/Daniel Marthin mengamankan gelar juara Taipei Open ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676799/john-herdman-laga-lawan-vietnam-peluang-indonesia-ambil-kendali-grup</t>
+          <t>https://www.antaranews.com/berita/5676584/leo-daniel-amankan-gelar-juarataipei-open-2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/f830ddbf-3b22-4a67-a02e-07a3ccba455c.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/badminton.jpg</t>
         </is>
       </c>
     </row>
@@ -509,94 +509,94 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Basarnas: 232 korban KMP Mutiara Santosa 2 dievakuasi lima meninggal</t>
+          <t>John Herdman: Laga lawan Vietnam peluang Indonesia ambil kendali grup</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 20:58:10 +0700</t>
+          <t>Sun, 02 Aug 2026 20:58:18 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Badan SAR Nasional (Basarnas) menyatakan sebanyak 232 korban kebakaran KMP Mutiara Santosa 2 di Perairan Utara Sumenep, ...</t>
+          <t>Pelatih tim nasional Indonesia John Herdman menyebut laga skuadnya menghadapi Vietnam pada lanjutan ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676796/basarnas-232-korban-kmp-mutiara-santosa-2-dievakuasi-lima-meninggal</t>
+          <t>https://www.antaranews.com/berita/5676799/john-herdman-laga-lawan-vietnam-peluang-indonesia-ambil-kendali-grup</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/1001118275_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/f830ddbf-3b22-4a67-a02e-07a3ccba455c.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>photo, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
+          <t>Basarnas: 232 korban KMP Mutiara Santosa 2 dievakuasi lima meninggal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
+          <t>Sun, 02 Aug 2026 20:58:10 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) ...</t>
+          <t>Badan SAR Nasional (Basarnas) menyatakan sebanyak 232 korban kebakaran KMP Mutiara Santosa 2 di Perairan Utara Sumenep, ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
+          <t>https://www.antaranews.com/berita/5676796/basarnas-232-korban-kmp-mutiara-santosa-2-dievakuasi-lima-meninggal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/1001118275_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>photo, top-news</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kepala BGN hentikan sementara SPPG Karangturi usai insiden pangan</t>
+          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 18:06:54 +0700</t>
+          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menghentikan sementara Satuan Pelayanan Pemenuhan Gizi (SPPG) Karangturi, ...</t>
+          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676704/kepala-bgn-hentikan-sementara-sppg-karangturi-usai-insiden-pangan</t>
+          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/upscalemedia-transformed-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>
@@ -608,28 +608,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Empat penumpang KMP Mutiara Sentosa 2 dilaporkan meninggal dunia</t>
+          <t>Kepala BGN hentikan sementara SPPG Karangturi usai insiden pangan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 18:03:19 +0700</t>
+          <t>Sun, 02 Aug 2026 18:06:54 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sebanyak empat penumpang Kapal Motor Penyeberangan (KMP) Mutiara Sentosa 2 dilaporkan meninggal dunia akibat kebakaran ...</t>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menghentikan sementara Satuan Pelayanan Pemenuhan Gizi (SPPG) Karangturi, ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676700/empat-penumpang-kmp-mutiara-sentosa-2-dilaporkan-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5676704/kepala-bgn-hentikan-sementara-sppg-karangturi-usai-insiden-pangan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/upscalemedia-transformed-5.jpg</t>
         </is>
       </c>
     </row>
@@ -641,28 +641,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tragedi Ceuta: 90 migran tewas saat menuju wilayah Spanyol dari Maroko</t>
+          <t>Empat penumpang KMP Mutiara Sentosa 2 dilaporkan meninggal dunia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:37:11 +0700</t>
+          <t>Sun, 02 Aug 2026 18:03:19 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jumlah migran yang tewas saat mencoba memasuki wilayah kantong Spanyol di Ceuta, Afrika Utara, dari Maroko mencapai 90 ...</t>
+          <t>Sebanyak empat penumpang Kapal Motor Penyeberangan (KMP) Mutiara Sentosa 2 dilaporkan meninggal dunia akibat kebakaran ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676688/tragedi-ceuta-90-migran-tewas-saat-menuju-wilayah-spanyol-dari-maroko</t>
+          <t>https://www.antaranews.com/berita/5676700/empat-penumpang-kmp-mutiara-sentosa-2-dilaporkan-meninggal-dunia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/thumbs_b_c_b45a072fcf2b0222189e4f1f5c2a3807.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>
@@ -674,28 +674,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Korban tewas gempa Jepang jadi 38 orang, ribuan warga masih mengungsi</t>
+          <t>Tragedi Ceuta: 90 migran tewas saat menuju wilayah Spanyol dari Maroko</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 16:02:01 +0700</t>
+          <t>Sun, 02 Aug 2026 17:37:11 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jumlah korban tewas akibat gempa bumi kuat yang mengguncang Prefektur Kumamoto di barat daya Jepang pekan lalu ...</t>
+          <t>Jumlah migran yang tewas saat mencoba memasuki wilayah kantong Spanyol di Ceuta, Afrika Utara, dari Maroko mencapai 90 ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676628/korban-tewas-gempa-jepang-jadi-38-orang-ribuan-warga-masih-mengungsi</t>
+          <t>https://www.antaranews.com/berita/5676688/tragedi-ceuta-90-migran-tewas-saat-menuju-wilayah-spanyol-dari-maroko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gempa-Bumi-Di-Kumamoto-Jepang-310726-JH-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/thumbs_b_c_b45a072fcf2b0222189e4f1f5c2a3807.jpg</t>
         </is>
       </c>
     </row>
@@ -707,28 +707,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>William Zepeda atasi Roach untuk rebut sabuk juara dunia WBC</t>
+          <t>Korban tewas gempa Jepang jadi 38 orang, ribuan warga masih mengungsi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 16:01:55 +0700</t>
+          <t>Sun, 02 Aug 2026 16:02:01 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petinju William Zepeda mengatasi Lamont Roach Jr dengan kemenangan angka untuk merebut sabuk juara dunia kelas ringan ...</t>
+          <t>Jumlah korban tewas akibat gempa bumi kuat yang mengguncang Prefektur Kumamoto di barat daya Jepang pekan lalu ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676625/william-zepeda-atasi-roach-untuk-rebut-sabuk-juara-dunia-wbc</t>
+          <t>https://www.antaranews.com/berita/5676628/korban-tewas-gempa-jepang-jadi-38-orang-ribuan-warga-masih-mengungsi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/4f02b6dc-36cc-44b4-aa19-5f8b74c51425.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gempa-Bumi-Di-Kumamoto-Jepang-310726-JH-3.jpg</t>
         </is>
       </c>
     </row>
@@ -740,28 +740,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Israel serang Gaza lagi meski sepakat lanjutkan gencatan senjata</t>
+          <t>William Zepeda atasi Roach untuk rebut sabuk juara dunia WBC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 15:58:04 +0700</t>
+          <t>Sun, 02 Aug 2026 16:01:55 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Delapan warga Palestina, termasuk dua anak, tewas dalam serangkaian serangan udara Israel di seluruh Jalur Gaza pada ...</t>
+          <t>Petinju William Zepeda mengatasi Lamont Roach Jr dengan kemenangan angka untuk merebut sabuk juara dunia kelas ringan ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676624/israel-serang-gaza-lagi-meski-sepakat-lanjutkan-gencatan-senjata</t>
+          <t>https://www.antaranews.com/berita/5676625/william-zepeda-atasi-roach-untuk-rebut-sabuk-juara-dunia-wbc</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/4f02b6dc-36cc-44b4-aa19-5f8b74c51425.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Leo/Daniel amankan gelar juaraTaipei Open 2026</t>
+          <t>Israel serang Gaza lagi meski sepakat lanjutkan gencatan senjata</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 15:12:06 +0700</t>
+          <t>Sun, 02 Aug 2026 15:58:04 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pebulu tangkis ganda putra Indonesia Leo Rolly Carnando/Daniel Marthin mengamankan gelar juara Taipei Open ...</t>
+          <t>Delapan warga Palestina, termasuk dua anak, tewas dalam serangkaian serangan udara Israel di seluruh Jalur Gaza pada ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676584/leo-daniel-amankan-gelar-juarataipei-open-2026</t>
+          <t>https://www.antaranews.com/berita/5676624/israel-serang-gaza-lagi-meski-sepakat-lanjutkan-gencatan-senjata</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/badminton.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-02.xlsx
+++ b/data/berita_antara_2026-08-02.xlsx
@@ -509,28 +509,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>John Herdman: Laga lawan Vietnam peluang Indonesia ambil kendali grup</t>
+          <t>Israel serang Gaza lagi meski sepakat lanjutkan gencatan senjata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 20:58:18 +0700</t>
+          <t>Sun, 02 Aug 2026 15:58:04 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional Indonesia John Herdman menyebut laga skuadnya menghadapi Vietnam pada lanjutan ...</t>
+          <t>Delapan warga Palestina, termasuk dua anak, tewas dalam serangkaian serangan udara Israel di seluruh Jalur Gaza pada ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676799/john-herdman-laga-lawan-vietnam-peluang-indonesia-ambil-kendali-grup</t>
+          <t>https://www.antaranews.com/berita/5676624/israel-serang-gaza-lagi-meski-sepakat-lanjutkan-gencatan-senjata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/f830ddbf-3b22-4a67-a02e-07a3ccba455c.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
         </is>
       </c>
     </row>
@@ -542,94 +542,94 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Basarnas: 232 korban KMP Mutiara Santosa 2 dievakuasi lima meninggal</t>
+          <t>John Herdman: Laga lawan Vietnam peluang Indonesia ambil kendali grup</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 20:58:10 +0700</t>
+          <t>Sun, 02 Aug 2026 20:58:18 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Badan SAR Nasional (Basarnas) menyatakan sebanyak 232 korban kebakaran KMP Mutiara Santosa 2 di Perairan Utara Sumenep, ...</t>
+          <t>Pelatih tim nasional Indonesia John Herdman menyebut laga skuadnya menghadapi Vietnam pada lanjutan ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676796/basarnas-232-korban-kmp-mutiara-santosa-2-dievakuasi-lima-meninggal</t>
+          <t>https://www.antaranews.com/berita/5676799/john-herdman-laga-lawan-vietnam-peluang-indonesia-ambil-kendali-grup</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/1001118275_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/f830ddbf-3b22-4a67-a02e-07a3ccba455c.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>photo, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
+          <t>Basarnas: 232 korban KMP Mutiara Santosa 2 dievakuasi lima meninggal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
+          <t>Sun, 02 Aug 2026 20:58:10 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) ...</t>
+          <t>Badan SAR Nasional (Basarnas) menyatakan sebanyak 232 korban kebakaran KMP Mutiara Santosa 2 di Perairan Utara Sumenep, ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
+          <t>https://www.antaranews.com/berita/5676796/basarnas-232-korban-kmp-mutiara-santosa-2-dievakuasi-lima-meninggal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/1001118275_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>photo, top-news</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kepala BGN hentikan sementara SPPG Karangturi usai insiden pangan</t>
+          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 18:06:54 +0700</t>
+          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menghentikan sementara Satuan Pelayanan Pemenuhan Gizi (SPPG) Karangturi, ...</t>
+          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676704/kepala-bgn-hentikan-sementara-sppg-karangturi-usai-insiden-pangan</t>
+          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/upscalemedia-transformed-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>
@@ -641,28 +641,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Empat penumpang KMP Mutiara Sentosa 2 dilaporkan meninggal dunia</t>
+          <t>Kepala BGN hentikan sementara SPPG Karangturi usai insiden pangan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 18:03:19 +0700</t>
+          <t>Sun, 02 Aug 2026 18:06:54 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sebanyak empat penumpang Kapal Motor Penyeberangan (KMP) Mutiara Sentosa 2 dilaporkan meninggal dunia akibat kebakaran ...</t>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menghentikan sementara Satuan Pelayanan Pemenuhan Gizi (SPPG) Karangturi, ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676700/empat-penumpang-kmp-mutiara-sentosa-2-dilaporkan-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5676704/kepala-bgn-hentikan-sementara-sppg-karangturi-usai-insiden-pangan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/upscalemedia-transformed-5.jpg</t>
         </is>
       </c>
     </row>
@@ -674,28 +674,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tragedi Ceuta: 90 migran tewas saat menuju wilayah Spanyol dari Maroko</t>
+          <t>Empat penumpang KMP Mutiara Sentosa 2 dilaporkan meninggal dunia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:37:11 +0700</t>
+          <t>Sun, 02 Aug 2026 18:03:19 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jumlah migran yang tewas saat mencoba memasuki wilayah kantong Spanyol di Ceuta, Afrika Utara, dari Maroko mencapai 90 ...</t>
+          <t>Sebanyak empat penumpang Kapal Motor Penyeberangan (KMP) Mutiara Sentosa 2 dilaporkan meninggal dunia akibat kebakaran ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676688/tragedi-ceuta-90-migran-tewas-saat-menuju-wilayah-spanyol-dari-maroko</t>
+          <t>https://www.antaranews.com/berita/5676700/empat-penumpang-kmp-mutiara-sentosa-2-dilaporkan-meninggal-dunia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/thumbs_b_c_b45a072fcf2b0222189e4f1f5c2a3807.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>
@@ -707,28 +707,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Korban tewas gempa Jepang jadi 38 orang, ribuan warga masih mengungsi</t>
+          <t>Tragedi Ceuta: 90 migran tewas saat menuju wilayah Spanyol dari Maroko</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 16:02:01 +0700</t>
+          <t>Sun, 02 Aug 2026 17:37:11 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jumlah korban tewas akibat gempa bumi kuat yang mengguncang Prefektur Kumamoto di barat daya Jepang pekan lalu ...</t>
+          <t>Jumlah migran yang tewas saat mencoba memasuki wilayah kantong Spanyol di Ceuta, Afrika Utara, dari Maroko mencapai 90 ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676628/korban-tewas-gempa-jepang-jadi-38-orang-ribuan-warga-masih-mengungsi</t>
+          <t>https://www.antaranews.com/berita/5676688/tragedi-ceuta-90-migran-tewas-saat-menuju-wilayah-spanyol-dari-maroko</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gempa-Bumi-Di-Kumamoto-Jepang-310726-JH-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/thumbs_b_c_b45a072fcf2b0222189e4f1f5c2a3807.jpg</t>
         </is>
       </c>
     </row>
@@ -740,28 +740,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>William Zepeda atasi Roach untuk rebut sabuk juara dunia WBC</t>
+          <t>Korban tewas gempa Jepang jadi 38 orang, ribuan warga masih mengungsi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 16:01:55 +0700</t>
+          <t>Sun, 02 Aug 2026 16:02:01 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petinju William Zepeda mengatasi Lamont Roach Jr dengan kemenangan angka untuk merebut sabuk juara dunia kelas ringan ...</t>
+          <t>Jumlah korban tewas akibat gempa bumi kuat yang mengguncang Prefektur Kumamoto di barat daya Jepang pekan lalu ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676625/william-zepeda-atasi-roach-untuk-rebut-sabuk-juara-dunia-wbc</t>
+          <t>https://www.antaranews.com/berita/5676628/korban-tewas-gempa-jepang-jadi-38-orang-ribuan-warga-masih-mengungsi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/4f02b6dc-36cc-44b4-aa19-5f8b74c51425.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gempa-Bumi-Di-Kumamoto-Jepang-310726-JH-3.jpg</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Israel serang Gaza lagi meski sepakat lanjutkan gencatan senjata</t>
+          <t>William Zepeda atasi Roach untuk rebut sabuk juara dunia WBC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 15:58:04 +0700</t>
+          <t>Sun, 02 Aug 2026 16:01:55 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Delapan warga Palestina, termasuk dua anak, tewas dalam serangkaian serangan udara Israel di seluruh Jalur Gaza pada ...</t>
+          <t>Petinju William Zepeda mengatasi Lamont Roach Jr dengan kemenangan angka untuk merebut sabuk juara dunia kelas ringan ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676624/israel-serang-gaza-lagi-meski-sepakat-lanjutkan-gencatan-senjata</t>
+          <t>https://www.antaranews.com/berita/5676625/william-zepeda-atasi-roach-untuk-rebut-sabuk-juara-dunia-wbc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/4f02b6dc-36cc-44b4-aa19-5f8b74c51425.jpeg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-02.xlsx
+++ b/data/berita_antara_2026-08-02.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apa Itu digital detox? manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
+          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">

--- a/data/berita_antara_2026-08-02.xlsx
+++ b/data/berita_antara_2026-08-02.xlsx
@@ -603,33 +603,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>photo, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
+          <t>Kepala BGN hentikan sementara SPPG Karangturi usai insiden pangan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
+          <t>Sun, 02 Aug 2026 18:06:54 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) ...</t>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menghentikan sementara Satuan Pelayanan Pemenuhan Gizi (SPPG) Karangturi, ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
+          <t>https://www.antaranews.com/berita/5676704/kepala-bgn-hentikan-sementara-sppg-karangturi-usai-insiden-pangan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/upscalemedia-transformed-5.jpg</t>
         </is>
       </c>
     </row>
@@ -641,28 +641,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kepala BGN hentikan sementara SPPG Karangturi usai insiden pangan</t>
+          <t>Empat penumpang KMP Mutiara Sentosa 2 dilaporkan meninggal dunia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 18:06:54 +0700</t>
+          <t>Sun, 02 Aug 2026 18:03:19 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menghentikan sementara Satuan Pelayanan Pemenuhan Gizi (SPPG) Karangturi, ...</t>
+          <t>Sebanyak empat penumpang Kapal Motor Penyeberangan (KMP) Mutiara Sentosa 2 dilaporkan meninggal dunia akibat kebakaran ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676704/kepala-bgn-hentikan-sementara-sppg-karangturi-usai-insiden-pangan</t>
+          <t>https://www.antaranews.com/berita/5676700/empat-penumpang-kmp-mutiara-sentosa-2-dilaporkan-meninggal-dunia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/upscalemedia-transformed-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>
@@ -674,28 +674,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empat penumpang KMP Mutiara Sentosa 2 dilaporkan meninggal dunia</t>
+          <t>Tragedi Ceuta: 90 migran tewas saat menuju wilayah Spanyol dari Maroko</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 18:03:19 +0700</t>
+          <t>Sun, 02 Aug 2026 17:37:11 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sebanyak empat penumpang Kapal Motor Penyeberangan (KMP) Mutiara Sentosa 2 dilaporkan meninggal dunia akibat kebakaran ...</t>
+          <t>Jumlah migran yang tewas saat mencoba memasuki wilayah kantong Spanyol di Ceuta, Afrika Utara, dari Maroko mencapai 90 ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676700/empat-penumpang-kmp-mutiara-sentosa-2-dilaporkan-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5676688/tragedi-ceuta-90-migran-tewas-saat-menuju-wilayah-spanyol-dari-maroko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/thumbs_b_c_b45a072fcf2b0222189e4f1f5c2a3807.jpg</t>
         </is>
       </c>
     </row>
@@ -707,28 +707,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tragedi Ceuta: 90 migran tewas saat menuju wilayah Spanyol dari Maroko</t>
+          <t>Korban tewas gempa Jepang jadi 38 orang, ribuan warga masih mengungsi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:37:11 +0700</t>
+          <t>Sun, 02 Aug 2026 16:02:01 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jumlah migran yang tewas saat mencoba memasuki wilayah kantong Spanyol di Ceuta, Afrika Utara, dari Maroko mencapai 90 ...</t>
+          <t>Jumlah korban tewas akibat gempa bumi kuat yang mengguncang Prefektur Kumamoto di barat daya Jepang pekan lalu ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676688/tragedi-ceuta-90-migran-tewas-saat-menuju-wilayah-spanyol-dari-maroko</t>
+          <t>https://www.antaranews.com/berita/5676628/korban-tewas-gempa-jepang-jadi-38-orang-ribuan-warga-masih-mengungsi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/thumbs_b_c_b45a072fcf2b0222189e4f1f5c2a3807.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gempa-Bumi-Di-Kumamoto-Jepang-310726-JH-3.jpg</t>
         </is>
       </c>
     </row>
@@ -740,61 +740,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Korban tewas gempa Jepang jadi 38 orang, ribuan warga masih mengungsi</t>
+          <t>William Zepeda atasi Roach untuk rebut sabuk juara dunia WBC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 16:02:01 +0700</t>
+          <t>Sun, 02 Aug 2026 16:01:55 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jumlah korban tewas akibat gempa bumi kuat yang mengguncang Prefektur Kumamoto di barat daya Jepang pekan lalu ...</t>
+          <t>Petinju William Zepeda mengatasi Lamont Roach Jr dengan kemenangan angka untuk merebut sabuk juara dunia kelas ringan ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676628/korban-tewas-gempa-jepang-jadi-38-orang-ribuan-warga-masih-mengungsi</t>
+          <t>https://www.antaranews.com/berita/5676625/william-zepeda-atasi-roach-untuk-rebut-sabuk-juara-dunia-wbc</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gempa-Bumi-Di-Kumamoto-Jepang-310726-JH-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/4f02b6dc-36cc-44b4-aa19-5f8b74c51425.jpeg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>William Zepeda atasi Roach untuk rebut sabuk juara dunia WBC</t>
+          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 16:01:55 +0700</t>
+          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Petinju William Zepeda mengatasi Lamont Roach Jr dengan kemenangan angka untuk merebut sabuk juara dunia kelas ringan ...</t>
+          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676625/william-zepeda-atasi-roach-untuk-rebut-sabuk-juara-dunia-wbc</t>
+          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/4f02b6dc-36cc-44b4-aa19-5f8b74c51425.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
         </is>
       </c>
     </row>
@@ -806,61 +806,61 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
+          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
+          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
+          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
+          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
+          <t>Walikota Samarinda dorong reformasi fiskal siasati penurunan anggaran</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
+          <t>Sun, 02 Aug 2026 14:50:44 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
+          <t>Wali Kota Samarinda, Andi Harun, mendorong reformasi fiskal melalui efisiensi dan penguatan Pendapatan Asli Daerah ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5676560/walikota-samarinda-dorong-reformasi-fiskal-siasati-penurunan-anggaran</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/IMG_3529.jpeg</t>
         </is>
       </c>
     </row>
@@ -872,61 +872,61 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Walikota Samarinda dorong reformasi fiskal siasati penurunan anggaran</t>
+          <t>Pemprov Sulteng beri insentif pajak kendaraan bermotor mulai 3 Agustus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 14:50:44 +0700</t>
+          <t>Sun, 02 Aug 2026 09:54:26 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wali Kota Samarinda, Andi Harun, mendorong reformasi fiskal melalui efisiensi dan penguatan Pendapatan Asli Daerah ...</t>
+          <t>Pemerintah Provinsi Sulawesi Tengah memberikan insentif pajak kendaraan bermotor (PKB) sebagai upaya meringankan beban ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676560/walikota-samarinda-dorong-reformasi-fiskal-siasati-penurunan-anggaran</t>
+          <t>https://www.antaranews.com/berita/5676349/pemprov-sulteng-beri-insentif-pajak-kendaraan-bermotor-mulai-3-agustus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/IMG_3529.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/IMG-20260802-WA0001.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pemprov Sulteng beri insentif pajak kendaraan bermotor mulai 3 Agustus</t>
+          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 09:54:26 +0700</t>
+          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Sulawesi Tengah memberikan insentif pajak kendaraan bermotor (PKB) sebagai upaya meringankan beban ...</t>
+          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676349/pemprov-sulteng-beri-insentif-pajak-kendaraan-bermotor-mulai-3-agustus</t>
+          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/IMG-20260802-WA0001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
         </is>
       </c>
     </row>
@@ -938,61 +938,61 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
+          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
+          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
+          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
+          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
+          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
+          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
+          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
         </is>
       </c>
     </row>
@@ -1004,28 +1004,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
+          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
+          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
+          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
+          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
+          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
+          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
+          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,28 +1070,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
+          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
+          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
+          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1103,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
+          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
+          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
+          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
+          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
         </is>
       </c>
     </row>
@@ -1136,28 +1136,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
+          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
+          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
+          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
         </is>
       </c>
     </row>
@@ -1169,28 +1169,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
+          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
+          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
+          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
+          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
         </is>
       </c>
     </row>
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
+          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
+          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
+          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
+          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
         </is>
       </c>
     </row>
@@ -1235,28 +1235,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
+          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
+          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
+          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
+          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
         </is>
       </c>
     </row>
@@ -1268,28 +1268,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
+          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
+          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
+          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
         </is>
       </c>
     </row>
@@ -1301,28 +1301,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
+          <t>10 barang wajib dibawa saat liburan agar perjalanan nyaman dan praktis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
+          <t>Sun, 02 Aug 2026 10:00:42 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
+          <t>Liburan menjadi momen yang dinantikan banyak orang untuk melepas penat dari rutinitas sehari-hari. Namun, perjalanan ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
+          <t>https://www.antaranews.com/berita/5676355/10-barang-wajib-dibawa-saat-liburan-agar-perjalanan-nyaman-dan-praktis</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000887286.jpg</t>
         </is>
       </c>
     </row>
@@ -1334,61 +1334,61 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10 barang wajib dibawa saat liburan agar perjalanan nyaman dan praktis</t>
+          <t>10 cara mengatur keuangan bulanan agar gaji tidak cepat habis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:00:42 +0700</t>
+          <t>Sun, 02 Aug 2026 09:54:58 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liburan menjadi momen yang dinantikan banyak orang untuk melepas penat dari rutinitas sehari-hari. Namun, perjalanan ...</t>
+          <t>Mengelola keuangan bulanan menjadi tantangan bagi banyak orang, terutama saat pengeluaran terasa lebih besar daripada ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676355/10-barang-wajib-dibawa-saat-liburan-agar-perjalanan-nyaman-dan-praktis</t>
+          <t>https://www.antaranews.com/berita/5676352/10-cara-mengatur-keuangan-bulanan-agar-gaji-tidak-cepat-habis</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000887286.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Ilustrasi-mengatur-keuangan.jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>tekno</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10 cara mengatur keuangan bulanan agar gaji tidak cepat habis</t>
+          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 09:54:58 +0700</t>
+          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mengelola keuangan bulanan menjadi tantangan bagi banyak orang, terutama saat pengeluaran terasa lebih besar daripada ...</t>
+          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676352/10-cara-mengatur-keuangan-bulanan-agar-gaji-tidak-cepat-habis</t>
+          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Ilustrasi-mengatur-keuangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
         </is>
       </c>
     </row>
@@ -1400,61 +1400,61 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
+          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
+          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
+          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
+          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
+          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
+          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
+          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
+          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
         </is>
       </c>
     </row>
@@ -1466,28 +1466,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
+          <t>Latihan Timnas Indonesia jelang lawan Vietnam</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
+          <t>Sun, 02 Aug 2026 21:09:02 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
+          <t>Sejumlah pesepak bola Timnas Indonesia mengikuti sesi latihan di Stadion GBK, Jakarta, Minggu (2/8/2026). Latihan Timnas Indonesia untuk persiapan laga ketiga Grup A Piala AFF 2026 melawan Vietnam di Stadion Pakansari pada Senin (3/8/2026). ANTARA FOTO/Fakhri Hermansyah/sgd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
+          <t>https://www.antaranews.com/foto/5676812/latihan-timnas-indonesia-jelang-lawan-vietnam</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Latihan-Timnas-Indonesia-jelang-melawan-Vietnam-020826-Fah-4.jpg</t>
         </is>
       </c>
     </row>
@@ -1499,28 +1499,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Latihan Timnas Indonesia jelang lawan Vietnam</t>
+          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:09:02 +0700</t>
+          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sejumlah pesepak bola Timnas Indonesia mengikuti sesi latihan di Stadion GBK, Jakarta, Minggu (2/8/2026). Latihan Timnas Indonesia untuk persiapan laga ketiga Grup A Piala AFF 2026 melawan Vietnam di Stadion Pakansari pada Senin (3/8/2026). ANTARA FOTO/Fakhri Hermansyah/sgd</t>
+          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) Mutiara Sentosa 2 yang berpenumpang sekitar 250 orang penumpang tersebut mengalami kebakaran saat melakukan pelayaran dari Surabaya ke Makassar. ANTARAFOTO/Umarul Faruq/sgd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676812/latihan-timnas-indonesia-jelang-lawan-vietnam</t>
+          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Latihan-Timnas-Indonesia-jelang-melawan-Vietnam-020826-Fah-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-02.xlsx
+++ b/data/berita_antara_2026-08-02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -429,6 +429,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,11 @@
           <t>URL Gambar</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/badminton.jpg</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,6 +540,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -566,6 +574,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/f830ddbf-3b22-4a67-a02e-07a3ccba455c.jpg</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -599,6 +608,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/1001118275_1.jpg</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -632,6 +642,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/upscalemedia-transformed-5.jpg</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -665,6 +676,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -698,6 +710,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/thumbs_b_c_b45a072fcf2b0222189e4f1f5c2a3807.jpg</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -731,6 +744,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gempa-Bumi-Di-Kumamoto-Jepang-310726-JH-3.jpg</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -764,334 +778,361 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/4f02b6dc-36cc-44b4-aa19-5f8b74c51425.jpeg</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
+          <t>Walikota Samarinda dorong reformasi fiskal siasati penurunan anggaran</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
+          <t>Sun, 02 Aug 2026 14:50:44 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
+          <t>Wali Kota Samarinda, Andi Harun, mendorong reformasi fiskal melalui efisiensi dan penguatan Pendapatan Asli Daerah ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
+          <t>https://www.antaranews.com/berita/5676560/walikota-samarinda-dorong-reformasi-fiskal-siasati-penurunan-anggaran</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/IMG_3529.jpeg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
+          <t>Pemprov Sulteng beri insentif pajak kendaraan bermotor mulai 3 Agustus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
+          <t>Sun, 02 Aug 2026 09:54:26 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
+          <t>Pemerintah Provinsi Sulawesi Tengah memberikan insentif pajak kendaraan bermotor (PKB) sebagai upaya meringankan beban ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5676349/pemprov-sulteng-beri-insentif-pajak-kendaraan-bermotor-mulai-3-agustus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/IMG-20260802-WA0001.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Walikota Samarinda dorong reformasi fiskal siasati penurunan anggaran</t>
+          <t>Praktik open dumping TPST Bantargebang mulai dihentikan per agustus 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 14:50:44 +0700</t>
+          <t>Sun, 02 Aug 2026 13:39:18 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wali Kota Samarinda, Andi Harun, mendorong reformasi fiskal melalui efisiensi dan penguatan Pendapatan Asli Daerah ...</t>
+          <t>Foto udara sejumlah truk melintas di dekat tumpukan sampah yang ditutup dengan media pelindung di Tempat Pembuangan Sampah Terpadu (TPST) Bantargebang, Cikiwul, Kota Bekasi, Jawa Barat, Minggu (2/8/2026). Pemerintah Provinsi DKI Jakarta mulai menerapkan sistem controlled landfill di TPST Bantargebang secara bertahap sejak 1 Agustus 2026 sebagai bagian dari penghentian praktik open dumping atau pembuangan sampah secara terbuka guna mewujudkan pengelolaan sampah yang lebih ramah lingkungan, meminimalkan risiko kebakaran, dan mengurangi bau. ANTARA FOTO/Darryl Ramadhan/nym.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676560/walikota-samarinda-dorong-reformasi-fiskal-siasati-penurunan-anggaran</t>
+          <t>https://www.antaranews.com/foto/5676521/praktik-open-dumping-tpst-bantargebang-mulai-dihentikan-per-agustus-2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/IMG_3529.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Pemprov-DKI-hentikan-sistem-Open-Dumping-di-TPST-Bantargebang-020826-ryl-5.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pemprov Sulteng beri insentif pajak kendaraan bermotor mulai 3 Agustus</t>
+          <t>Air menyusut akibat kemarau, hamparan pasir muncul di Sungai Batang Tembesi Jambi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 09:54:26 +0700</t>
+          <t>Sun, 02 Aug 2026 13:31:49 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Sulawesi Tengah memberikan insentif pajak kendaraan bermotor (PKB) sebagai upaya meringankan beban ...</t>
+          <t>Foto udara Sungai Batang Tembesi yang airnya surut di Sarolangun, Jambi, Minggu (2/8/2026). Sungai yang menghilir ke Sungai Batanghari tersebut menyusut akibat kemarau dan memunculkan hamparan pasir hingga sepanjang 75 meter dari tepi atau hampir menutupi separuh alur sungai sejak tiga minggu terakhir. ANTARA FOTO/Wahdi Septiawan/nym.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676349/pemprov-sulteng-beri-insentif-pajak-kendaraan-bermotor-mulai-3-agustus</t>
+          <t>https://www.antaranews.com/foto/5676516/air-menyusut-akibat-kemarau-hamparan-pasir-muncul-di-sungai-batang-tembesi-jambi</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/IMG-20260802-WA0001.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Penyusutan-debit-air-Sungai-Batang-Tembesi-di-Sarolangun-020826-ws-4.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
+          <t>Lima pesepeda akan jelajahi lima provinsi kampanye perlindungan hutan dan orangutan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
+          <t>Sun, 02 Aug 2026 11:19:28 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
+          <t>Sejumlah peserta mengayuh sepeda saat pelepasan Ekspedisi Hutan Merdeka di kawasan Monas, Jakarta, Minggu (2/8/2026). Ekspedisi Hutan Merdeka yang diikuti lima pesepeda itu akan menempuh perjalanan sejauh 1.700 kilometer dengan melintasi lima provinsi di Pulau Sumatera sebagai kampanye perlindungan hutan dan orangutan. ANTARA FOTO/Dhemas Reviyanto/nym.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
+          <t>https://www.antaranews.com/foto/5676425/lima-pesepeda-akan-jelajahi-lima-provinsi-kampanye-perlindungan-hutan-dan-orangutan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/pelepasan-ekspedisi-hutan-merdeka-020826-dr-04.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
+          <t>Pertunjukan api ramaikan Festival Abad Pertengahan ke-14 di Kroasia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
+          <t>Sun, 02 Aug 2026 08:37:58 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
+          <t>Para pemain menunjukkan kepiawaian memainkan api dalam Festival Abad Pertengahan ke-14 di Kastil Morosini-Grimani di Svetvincenat, Kroasia, Jumat (31/7/2026). Festival ini berlangsung 31 Juli hingga 2 Agustus 2026 dengan menampilkan turnamen ksatria, pameran kerajinan kuno, dan pertunjukan api. ANTARA FOTO/PIXSELL via Xinhua/Srecko Niketic/nym.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/foto/5676319/pertunjukan-api-ramaikan-festival-abad-pertengahan-ke-14-di-kroasia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/CmxztpE000043_20260802_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
+          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
+          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
+          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
+          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
+          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
+          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
+          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
+          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
+          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
+          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
+          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
+          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
+          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
+          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1144,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
+          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
+          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
+          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1136,28 +1182,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
+          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
+          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
+          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
+          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1169,28 +1220,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
+          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
+          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
+          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
+          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1202,28 +1258,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
+          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
+          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
+          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
+          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1235,28 +1296,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
+          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
+          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
+          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1268,28 +1334,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
+          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
+          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
+          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
+          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1301,28 +1372,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10 barang wajib dibawa saat liburan agar perjalanan nyaman dan praktis</t>
+          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:00:42 +0700</t>
+          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liburan menjadi momen yang dinantikan banyak orang untuk melepas penat dari rutinitas sehari-hari. Namun, perjalanan ...</t>
+          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676355/10-barang-wajib-dibawa-saat-liburan-agar-perjalanan-nyaman-dan-praktis</t>
+          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000887286.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1334,226 +1410,261 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10 cara mengatur keuangan bulanan agar gaji tidak cepat habis</t>
+          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 09:54:58 +0700</t>
+          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mengelola keuangan bulanan menjadi tantangan bagi banyak orang, terutama saat pengeluaran terasa lebih besar daripada ...</t>
+          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676352/10-cara-mengatur-keuangan-bulanan-agar-gaji-tidak-cepat-habis</t>
+          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Ilustrasi-mengatur-keuangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
+          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
+          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
+          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
+          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
+          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
+          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
+          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
+          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
+          <t>10 barang wajib dibawa saat liburan agar perjalanan nyaman dan praktis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
+          <t>Sun, 02 Aug 2026 10:00:42 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
+          <t>Liburan menjadi momen yang dinantikan banyak orang untuk melepas penat dari rutinitas sehari-hari. Namun, perjalanan ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
+          <t>https://www.antaranews.com/berita/5676355/10-barang-wajib-dibawa-saat-liburan-agar-perjalanan-nyaman-dan-praktis</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000887286.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Latihan Timnas Indonesia jelang lawan Vietnam</t>
+          <t>10 cara mengatur keuangan bulanan agar gaji tidak cepat habis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:09:02 +0700</t>
+          <t>Sun, 02 Aug 2026 09:54:58 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sejumlah pesepak bola Timnas Indonesia mengikuti sesi latihan di Stadion GBK, Jakarta, Minggu (2/8/2026). Latihan Timnas Indonesia untuk persiapan laga ketiga Grup A Piala AFF 2026 melawan Vietnam di Stadion Pakansari pada Senin (3/8/2026). ANTARA FOTO/Fakhri Hermansyah/sgd</t>
+          <t>Mengelola keuangan bulanan menjadi tantangan bagi banyak orang, terutama saat pengeluaran terasa lebih besar daripada ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676812/latihan-timnas-indonesia-jelang-lawan-vietnam</t>
+          <t>https://www.antaranews.com/berita/5676352/10-cara-mengatur-keuangan-bulanan-agar-gaji-tidak-cepat-habis</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Latihan-Timnas-Indonesia-jelang-melawan-Vietnam-020826-Fah-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Ilustrasi-mengatur-keuangan.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>tekno</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
+          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
+          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) Mutiara Sentosa 2 yang berpenumpang sekitar 250 orang penumpang tersebut mengalami kebakaran saat melakukan pelayaran dari Surabaya ke Makassar. ANTARAFOTO/Umarul Faruq/sgd</t>
+          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
+          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>tekno</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Melihat balap babi di Amerika</t>
+          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:06:31 +0700</t>
+          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sejumlah babi berlomba dalam kompetisi balap babi pada Orange County Fair di Costa Mesa, California, Amerika Serikat, (1/8/2026). ANTARA FOTO/Xinhua/Qiu Chen/sgd</t>
+          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676656/melihat-balap-babi-di-amerika</t>
+          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/XxjpbeE000086_20260802_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1565,28 +1676,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Praktik open dumping TPST Bantargebang mulai dihentikan per agustus 2026</t>
+          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 13:39:18 +0700</t>
+          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Foto udara sejumlah truk melintas di dekat tumpukan sampah yang ditutup dengan media pelindung di Tempat Pembuangan Sampah Terpadu (TPST) Bantargebang, Cikiwul, Kota Bekasi, Jawa Barat, Minggu (2/8/2026). Pemerintah Provinsi DKI Jakarta mulai menerapkan sistem controlled landfill di TPST Bantargebang secara bertahap sejak 1 Agustus 2026 sebagai bagian dari penghentian praktik open dumping atau pembuangan sampah secara terbuka guna mewujudkan pengelolaan sampah yang lebih ramah lingkungan, meminimalkan risiko kebakaran, dan mengurangi bau. ANTARA FOTO/Darryl Ramadhan/nym.</t>
+          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676521/praktik-open-dumping-tpst-bantargebang-mulai-dihentikan-per-agustus-2026</t>
+          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Pemprov-DKI-hentikan-sistem-Open-Dumping-di-TPST-Bantargebang-020826-ryl-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1598,28 +1714,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Air menyusut akibat kemarau, hamparan pasir muncul di Sungai Batang Tembesi Jambi</t>
+          <t>Latihan Timnas Indonesia jelang lawan Vietnam</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 13:31:49 +0700</t>
+          <t>Sun, 02 Aug 2026 21:09:02 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Foto udara Sungai Batang Tembesi yang airnya surut di Sarolangun, Jambi, Minggu (2/8/2026). Sungai yang menghilir ke Sungai Batanghari tersebut menyusut akibat kemarau dan memunculkan hamparan pasir hingga sepanjang 75 meter dari tepi atau hampir menutupi separuh alur sungai sejak tiga minggu terakhir. ANTARA FOTO/Wahdi Septiawan/nym.</t>
+          <t>Sejumlah pesepak bola Timnas Indonesia mengikuti sesi latihan di Stadion GBK, Jakarta, Minggu (2/8/2026). Latihan Timnas Indonesia untuk persiapan laga ketiga Grup A Piala AFF 2026 melawan Vietnam di Stadion Pakansari pada Senin (3/8/2026). ANTARA FOTO/Fakhri Hermansyah/sgd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676516/air-menyusut-akibat-kemarau-hamparan-pasir-muncul-di-sungai-batang-tembesi-jambi</t>
+          <t>https://www.antaranews.com/foto/5676812/latihan-timnas-indonesia-jelang-lawan-vietnam</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Penyusutan-debit-air-Sungai-Batang-Tembesi-di-Sarolangun-020826-ws-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Latihan-Timnas-Indonesia-jelang-melawan-Vietnam-020826-Fah-4.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1631,28 +1752,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lima pesepeda akan jelajahi lima provinsi kampanye perlindungan hutan dan orangutan</t>
+          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:19:28 +0700</t>
+          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sejumlah peserta mengayuh sepeda saat pelepasan Ekspedisi Hutan Merdeka di kawasan Monas, Jakarta, Minggu (2/8/2026). Ekspedisi Hutan Merdeka yang diikuti lima pesepeda itu akan menempuh perjalanan sejauh 1.700 kilometer dengan melintasi lima provinsi di Pulau Sumatera sebagai kampanye perlindungan hutan dan orangutan. ANTARA FOTO/Dhemas Reviyanto/nym.</t>
+          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) Mutiara Sentosa 2 yang berpenumpang sekitar 250 orang penumpang tersebut mengalami kebakaran saat melakukan pelayaran dari Surabaya ke Makassar. ANTARAFOTO/Umarul Faruq/sgd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676425/lima-pesepeda-akan-jelajahi-lima-provinsi-kampanye-perlindungan-hutan-dan-orangutan</t>
+          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/pelepasan-ekspedisi-hutan-merdeka-020826-dr-04.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1664,33 +1790,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pertunjukan api ramaikan Festival Abad Pertengahan ke-14 di Kroasia</t>
+          <t>Melihat balap babi di Amerika</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 08:37:58 +0700</t>
+          <t>Sun, 02 Aug 2026 17:06:31 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Para pemain menunjukkan kepiawaian memainkan api dalam Festival Abad Pertengahan ke-14 di Kastil Morosini-Grimani di Svetvincenat, Kroasia, Jumat (31/7/2026). Festival ini berlangsung 31 Juli hingga 2 Agustus 2026 dengan menampilkan turnamen ksatria, pameran kerajinan kuno, dan pertunjukan api. ANTARA FOTO/PIXSELL via Xinhua/Srecko Niketic/nym.</t>
+          <t>Sejumlah babi berlomba dalam kompetisi balap babi pada Orange County Fair di Costa Mesa, California, Amerika Serikat, (1/8/2026). ANTARA FOTO/Xinhua/Qiu Chen/sgd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676319/pertunjukan-api-ramaikan-festival-abad-pertengahan-ke-14-di-kroasia</t>
+          <t>https://www.antaranews.com/foto/5676656/melihat-balap-babi-di-amerika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/CmxztpE000043_20260802_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/XxjpbeE000086_20260802_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38"/>
+  <autoFilter ref="A1:H38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-02.xlsx
+++ b/data/berita_antara_2026-08-02.xlsx
@@ -987,33 +987,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
+          <t>Melihat balap babi di Amerika</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
+          <t>Sun, 02 Aug 2026 17:06:31 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
+          <t>Sejumlah babi berlomba dalam kompetisi balap babi pada Orange County Fair di Costa Mesa, California, Amerika Serikat, (1/8/2026). ANTARA FOTO/Xinhua/Qiu Chen/sgd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
+          <t>https://www.antaranews.com/foto/5676656/melihat-balap-babi-di-amerika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/XxjpbeE000086_20260802_PEPFN0A001.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1030,28 +1030,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
+          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
+          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
+          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1063,33 +1063,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
+          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
+          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
+          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
+          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1106,28 +1106,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
+          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
+          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
+          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1139,33 +1139,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
+          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
+          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
+          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
+          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1182,28 +1182,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
+          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
+          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
+          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1220,28 +1220,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
+          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
+          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
+          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1258,28 +1258,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
+          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
+          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
+          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
+          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1296,28 +1296,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
+          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
+          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
+          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1334,28 +1334,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
+          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
+          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
+          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
+          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1372,28 +1372,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
+          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
+          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
+          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
+          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1410,28 +1410,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
+          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
+          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
+          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
+          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1448,28 +1448,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
+          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
+          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
+          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1486,28 +1486,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
+          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
+          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
+          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
+          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1524,28 +1524,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10 barang wajib dibawa saat liburan agar perjalanan nyaman dan praktis</t>
+          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:00:42 +0700</t>
+          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liburan menjadi momen yang dinantikan banyak orang untuk melepas penat dari rutinitas sehari-hari. Namun, perjalanan ...</t>
+          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676355/10-barang-wajib-dibawa-saat-liburan-agar-perjalanan-nyaman-dan-praktis</t>
+          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000887286.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10 cara mengatur keuangan bulanan agar gaji tidak cepat habis</t>
+          <t>10 barang wajib dibawa saat liburan agar perjalanan nyaman dan praktis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 09:54:58 +0700</t>
+          <t>Sun, 02 Aug 2026 10:00:42 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mengelola keuangan bulanan menjadi tantangan bagi banyak orang, terutama saat pengeluaran terasa lebih besar daripada ...</t>
+          <t>Liburan menjadi momen yang dinantikan banyak orang untuk melepas penat dari rutinitas sehari-hari. Namun, perjalanan ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676352/10-cara-mengatur-keuangan-bulanan-agar-gaji-tidak-cepat-habis</t>
+          <t>https://www.antaranews.com/berita/5676355/10-barang-wajib-dibawa-saat-liburan-agar-perjalanan-nyaman-dan-praktis</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Ilustrasi-mengatur-keuangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000887286.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1595,33 +1595,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
+          <t>10 cara mengatur keuangan bulanan agar gaji tidak cepat habis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
+          <t>Sun, 02 Aug 2026 09:54:58 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
+          <t>Mengelola keuangan bulanan menjadi tantangan bagi banyak orang, terutama saat pengeluaran terasa lebih besar daripada ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
+          <t>https://www.antaranews.com/berita/5676352/10-cara-mengatur-keuangan-bulanan-agar-gaji-tidak-cepat-habis</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Ilustrasi-mengatur-keuangan.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1638,28 +1638,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
+          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
+          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
+          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
+          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1671,33 +1671,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>tekno</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
+          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
+          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
+          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
+          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1714,28 +1714,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Latihan Timnas Indonesia jelang lawan Vietnam</t>
+          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:09:02 +0700</t>
+          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sejumlah pesepak bola Timnas Indonesia mengikuti sesi latihan di Stadion GBK, Jakarta, Minggu (2/8/2026). Latihan Timnas Indonesia untuk persiapan laga ketiga Grup A Piala AFF 2026 melawan Vietnam di Stadion Pakansari pada Senin (3/8/2026). ANTARA FOTO/Fakhri Hermansyah/sgd</t>
+          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676812/latihan-timnas-indonesia-jelang-lawan-vietnam</t>
+          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Latihan-Timnas-Indonesia-jelang-melawan-Vietnam-020826-Fah-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1752,28 +1752,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
+          <t>Latihan Timnas Indonesia jelang lawan Vietnam</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
+          <t>Sun, 02 Aug 2026 21:09:02 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) Mutiara Sentosa 2 yang berpenumpang sekitar 250 orang penumpang tersebut mengalami kebakaran saat melakukan pelayaran dari Surabaya ke Makassar. ANTARAFOTO/Umarul Faruq/sgd</t>
+          <t>Sejumlah pesepak bola Timnas Indonesia mengikuti sesi latihan di Stadion GBK, Jakarta, Minggu (2/8/2026). Latihan Timnas Indonesia untuk persiapan laga ketiga Grup A Piala AFF 2026 melawan Vietnam di Stadion Pakansari pada Senin (3/8/2026). ANTARA FOTO/Fakhri Hermansyah/sgd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
+          <t>https://www.antaranews.com/foto/5676812/latihan-timnas-indonesia-jelang-lawan-vietnam</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Latihan-Timnas-Indonesia-jelang-melawan-Vietnam-020826-Fah-4.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1790,28 +1790,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Melihat balap babi di Amerika</t>
+          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:06:31 +0700</t>
+          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sejumlah babi berlomba dalam kompetisi balap babi pada Orange County Fair di Costa Mesa, California, Amerika Serikat, (1/8/2026). ANTARA FOTO/Xinhua/Qiu Chen/sgd</t>
+          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) Mutiara Sentosa 2 yang berpenumpang sekitar 250 orang penumpang tersebut mengalami kebakaran saat melakukan pelayaran dari Surabaya ke Makassar. ANTARAFOTO/Umarul Faruq/sgd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676656/melihat-balap-babi-di-amerika</t>
+          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/XxjpbeE000086_20260802_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">

--- a/data/berita_antara_2026-08-02.xlsx
+++ b/data/berita_antara_2026-08-02.xlsx
@@ -1025,33 +1025,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
+          <t>10 barang wajib dibawa saat liburan agar perjalanan nyaman dan praktis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
+          <t>Sun, 02 Aug 2026 10:00:42 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
+          <t>Liburan menjadi momen yang dinantikan banyak orang untuk melepas penat dari rutinitas sehari-hari. Namun, perjalanan ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
+          <t>https://www.antaranews.com/berita/5676355/10-barang-wajib-dibawa-saat-liburan-agar-perjalanan-nyaman-dan-praktis</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000887286.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1063,33 +1063,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
+          <t>10 cara mengatur keuangan bulanan agar gaji tidak cepat habis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
+          <t>Sun, 02 Aug 2026 09:54:58 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
+          <t>Mengelola keuangan bulanan menjadi tantangan bagi banyak orang, terutama saat pengeluaran terasa lebih besar daripada ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5676352/10-cara-mengatur-keuangan-bulanan-agar-gaji-tidak-cepat-habis</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Ilustrasi-mengatur-keuangan.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1101,33 +1101,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
+          <t>Latihan Timnas Indonesia jelang lawan Vietnam</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
+          <t>Sun, 02 Aug 2026 21:09:02 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
+          <t>Sejumlah pesepak bola Timnas Indonesia mengikuti sesi latihan di Stadion GBK, Jakarta, Minggu (2/8/2026). Latihan Timnas Indonesia untuk persiapan laga ketiga Grup A Piala AFF 2026 melawan Vietnam di Stadion Pakansari pada Senin (3/8/2026). ANTARA FOTO/Fakhri Hermansyah/sgd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
+          <t>https://www.antaranews.com/foto/5676812/latihan-timnas-indonesia-jelang-lawan-vietnam</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Latihan-Timnas-Indonesia-jelang-melawan-Vietnam-020826-Fah-4.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1139,33 +1139,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
+          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
+          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
+          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) Mutiara Sentosa 2 yang berpenumpang sekitar 250 orang penumpang tersebut mengalami kebakaran saat melakukan pelayaran dari Surabaya ke Makassar. ANTARAFOTO/Umarul Faruq/sgd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1177,33 +1177,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
+          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
+          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
+          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
+          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1215,33 +1215,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
+          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
+          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
+          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1253,33 +1253,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
+          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
+          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
+          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1291,33 +1291,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
+          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
+          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
+          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
+          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1334,28 +1334,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
+          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
+          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
+          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1372,28 +1372,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
+          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
+          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
+          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
+          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1410,28 +1410,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
+          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
+          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
+          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
+          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1448,28 +1448,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
+          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
+          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
+          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
+          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1486,28 +1486,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
+          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
+          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
+          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1524,28 +1524,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
+          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
+          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
+          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
+          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10 barang wajib dibawa saat liburan agar perjalanan nyaman dan praktis</t>
+          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:00:42 +0700</t>
+          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liburan menjadi momen yang dinantikan banyak orang untuk melepas penat dari rutinitas sehari-hari. Namun, perjalanan ...</t>
+          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676355/10-barang-wajib-dibawa-saat-liburan-agar-perjalanan-nyaman-dan-praktis</t>
+          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000887286.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1600,28 +1600,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10 cara mengatur keuangan bulanan agar gaji tidak cepat habis</t>
+          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 09:54:58 +0700</t>
+          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mengelola keuangan bulanan menjadi tantangan bagi banyak orang, terutama saat pengeluaran terasa lebih besar daripada ...</t>
+          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676352/10-cara-mengatur-keuangan-bulanan-agar-gaji-tidak-cepat-habis</t>
+          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Ilustrasi-mengatur-keuangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1633,33 +1633,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
+          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
+          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
+          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
+          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1671,33 +1671,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
+          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
+          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
+          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
+          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1709,33 +1709,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>tekno</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
+          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
+          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
+          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
+          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1747,33 +1747,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>tekno</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Latihan Timnas Indonesia jelang lawan Vietnam</t>
+          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:09:02 +0700</t>
+          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sejumlah pesepak bola Timnas Indonesia mengikuti sesi latihan di Stadion GBK, Jakarta, Minggu (2/8/2026). Latihan Timnas Indonesia untuk persiapan laga ketiga Grup A Piala AFF 2026 melawan Vietnam di Stadion Pakansari pada Senin (3/8/2026). ANTARA FOTO/Fakhri Hermansyah/sgd</t>
+          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676812/latihan-timnas-indonesia-jelang-lawan-vietnam</t>
+          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/Latihan-Timnas-Indonesia-jelang-melawan-Vietnam-020826-Fah-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1790,28 +1790,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 terbakar di perairan Sumenep</t>
+          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 19:00:25 +0700</t>
+          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kapal Mutiara Sentosa 2 terbakar di perairan Sumenep, Jawa Timur, Minggu (2/8/2026). Kapal Motor Penumpang (KMP) Mutiara Sentosa 2 yang berpenumpang sekitar 250 orang penumpang tersebut mengalami kebakaran saat melakukan pelayaran dari Surabaya ke Makassar. ANTARAFOTO/Umarul Faruq/sgd</t>
+          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676725/kmp-mutiara-sentosa-2-terbakar-di-perairan-sumenep</t>
+          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">

--- a/data/berita_antara_2026-08-02.xlsx
+++ b/data/berita_antara_2026-08-02.xlsx
@@ -1177,33 +1177,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
+          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
+          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
+          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
+          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1220,28 +1220,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
+          <t>4 contoh sambutan ketua panitia 17 Agustus 2026 singkat, formal, dan penuh makna</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
+          <t>Sun, 02 Aug 2026 11:04:26 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
+          <t>Peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 menjadi momentum bagi masyarakat untuk ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5676415/4-contoh-sambutan-ketua-panitia-17-agustus-2026-singkat-formal-dan-penuh-makna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/18/lomba-memerihakan-hut-kemerdekaan-ri-di-ciamis-2602537.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1253,33 +1253,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
+          <t>Cara daftar Upacara 17 Agustus 2026 di Istana Merdeka, simak syarat dan jadwalnya</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
+          <t>Sun, 02 Aug 2026 10:59:29 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
+          <t>Pemerintah belum mengumumkan jadwal resmi pembukaan pendaftaran peserta upacara peringatan HUT ke-81 Kemerdekaan ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
+          <t>https://www.antaranews.com/berita/5676408/cara-daftar-upacara-17-agustus-2026-di-istana-merdeka-simak-syarat-dan-jadwalnya</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/Upacara-Prasetya-Perwira-TNI-POLRI-22072026-gp-2.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1296,28 +1296,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
+          <t>Cara mencairkan bansos PKH dan BPNT Agustus 2026 lewat bank dan kantor pos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
+          <t>Sun, 02 Aug 2026 10:51:29 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
+          <t>Penyaluran bantuan sosial Program Keluarga Harapan (PKH) dan Bantuan Pangan Non Tunai (BPNT) periode Agustus 2026 ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676407/cara-mencairkan-bansos-pkh-dan-bpnt-agustus-2026-lewat-bank-dan-kantor-pos</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/27/IMG_20260327_142333.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1329,33 +1329,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
+          <t>NIK tidak ditemukan saat cek bansos? Ini 6 penyebab dan cara mengatasinya</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
+          <t>Sun, 02 Aug 2026 10:43:03 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
+          <t>Sebagian masyarakat masih mengalami kendala saat mengecek status penerima bantuan sosial (bansos), salah satunya muncul ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
+          <t>https://www.antaranews.com/berita/5676401/nik-tidak-ditemukan-saat-cek-bansos-ini-6-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/bansos-ngawi-1.jpeg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1372,28 +1372,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
+          <t>Waspada! Ini ciri-ciri kalau mata Anda mulai minus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
+          <t>Sun, 02 Aug 2026 23:27:26 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
+          <t>Miopi atau mata minus adalah gangguan refraksi yang menyebabkan seseorang kesulitan melihat benda yang berada di ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676920/waspada-ini-ciri-ciri-kalau-mata-anda-mulai-minus</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/03/27/antarafoto-safari-kesehatan-2024-270324-nhw-4.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1410,28 +1410,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
+          <t>Kenali ciri-ciri kecanduan PMO dan bagaimana cara mengatasinya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
+          <t>Sun, 02 Aug 2026 23:24:09 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
+          <t>Kecanduan PMO atau Pornography, Masturbation, Orgasm menjadi salah satu topik yang semakin banyak diperbincangkan, ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676919/kenali-ciri-ciri-kecanduan-pmo-dan-bagaimana-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1448,28 +1448,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
+          <t>Suka mual saat olahraga? Ini penyebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
+          <t>Sun, 02 Aug 2026 23:19:36 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
+          <t>Olahraga seharusnya membuat tubuh terasa lebih segar dan bugar. Namun, sebagian orang justru mengalami mual saat sedang ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
+          <t>https://www.antaranews.com/berita/5676912/suka-mual-saat-olahraga-ini-penyebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/05/02/stretching-498256_1280.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1486,28 +1486,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
+          <t>10 Makanan yang bagus untuk bulu kucing agar tetap lebat dan berkilau</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
+          <t>Sun, 02 Aug 2026 22:58:56 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
+          <t>Bulu yang lebat, halus, dan berkilau menjadi salah satu tanda bahwa kucing berada dalam kondisi sehat. Selain ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676901/10-makanan-yang-bagus-untuk-bulu-kucing-agar-tetap-lebat-dan-berkilau</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/08/16/IMG_1785.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1524,28 +1524,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
+          <t>Inilah 10 penyebab kucing tidak mau makan dan cara atasinya</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
+          <t>Sun, 02 Aug 2026 22:55:13 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
+          <t>Kucing yang tiba-tiba tidak mau makan tentu membuat pemiliknya khawatir. Pasalnya, nafsu makan merupakan salah satu ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
+          <t>https://www.antaranews.com/berita/5676893/inilah-10-penyebab-kucing-tidak-mau-makan-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/08/08/IMG_20210808_073426-01.jpeg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
+          <t>Apa Itu digital detox? Manfaat, cara memulai, dan dampaknya bagi kesehatan mental</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
+          <t>Sun, 02 Aug 2026 11:23:42 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
+          <t>Digital detox semakin banyak dibicarakan seiring meningkatnya kesadaran masyarakat terhadap dampak penggunaan gadget ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
+          <t>https://www.antaranews.com/berita/5676429/apa-itu-digital-detox-manfaat-cara-memulai-dan-dampaknya-bagi-kesehatan-mental</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/02/handphone.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1600,28 +1600,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
+          <t>7 manfaat baby oil untuk wajah serta cara menggunakannya dengan aman</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
+          <t>Sun, 02 Aug 2026 11:14:29 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
+          <t>Baby oil tidak hanya digunakan untuk perawatan kulit bayi, tetapi juga kerap dimanfaatkan sebagai bagian dari rutinitas ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
+          <t>https://www.antaranews.com/berita/5676420/7-manfaat-baby-oil-untuk-wajah-serta-cara-menggunakannya-dengan-aman</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/Tua.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1638,28 +1638,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
+          <t>20 ide hadiah lomba 17 Agustus 2026 yang murah, bermanfaat, dan menarik</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
+          <t>Sun, 02 Aug 2026 11:09:39 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
+          <t>Menjelang peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026, berbagai lingkungan mulai ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676419/20-ide-hadiah-lomba-17-agustus-2026-yang-murah-bermanfaat-dan-menarik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/17/pesta-rakyat-hut-ri-di-monas-2602245.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1676,28 +1676,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
+          <t>Kenapa badan sakit-sakit setelah gym? Ini sebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
+          <t>Sun, 02 Aug 2026 10:38:58 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
+          <t>Merasa badan pegal atau sakit-sakit setelah berolahraga di gym merupakan hal yang umum dialami, terutama oleh pemula ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
+          <t>https://www.antaranews.com/berita/5676396/kenapa-badan-sakit-sakit-setelah-gym-ini-sebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/indeks-pembangunan-manusia-kalimantan-barat-2670125.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1709,33 +1709,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
+          <t>10 tanda tubuh kekurangan air yang sering diabaikan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
+          <t>Sun, 02 Aug 2026 10:04:12 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
+          <t>Air merupakan komponen utama dalam tubuh manusia yang berperan penting dalam menjaga suhu tubuh, melancarkan sirkulasi ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
+          <t>https://www.antaranews.com/berita/5676363/10-tanda-tubuh-kekurangan-air-yang-sering-diabaikan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/Aqua-pic.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1752,28 +1752,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
+          <t>10 cara mengurangi screen time agar mata tetap sehat dan tidur nyenyak</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
+          <t>Sun, 02 Aug 2026 10:13:01 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
+          <t>Penggunaan ponsel, tablet, dan komputer telah menjadi bagian dari kehidupan sehari-hari. Mulai dari bekerja, belajar, ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
+          <t>https://www.antaranews.com/berita/5676376/10-cara-mengurangi-screen-time-agar-mata-tetap-sehat-dan-tidur-nyenyak</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/CDAD3117-892E-4E7F-AF44-CF43EED7F052.jpeg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1785,33 +1785,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>tekno</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Andi Sultan raih medali emas Asian Taekwondo Indonesia Open Championships</t>
+          <t>Cara tepat restart paksa iPhone yang error agar kembali normal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 21:13:46 +0700</t>
+          <t>Sun, 02 Aug 2026 10:09:15 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlet Taekwondo Indonesia Andi Sultan mengibarkan bendera Merah Putih usai memenangkan pertandingan final nomor Poomsae Freestyle Individual Men Over 17 pada 8th Asian Taekwondo Indonesia Open Championships 2026 di Tennis Indoor Senayan, Jakarta, Minggu (2/8/2026). Andi Sultan meraih medali emas dengan perolehan skor 8.540 poin. ANTARA FOTO/Dhemas Reviyanto/sgd</t>
+          <t>iPhone yang tiba-tiba error, layar tidak merespons sentuhan, atau berhenti di logo Apple menjadi masalah yang cukup ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676816/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships</t>
+          <t>https://www.antaranews.com/berita/5676373/cara-tepat-restart-paksa-iphone-yang-error-agar-kembali-normal</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-03.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/InShot_20260513_153025843.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
